--- a/HR_GENERATE_OFFER_LETTER_FILES_DISPACHER/Data/Input/CandidateInfo.xlsx
+++ b/HR_GENERATE_OFFER_LETTER_FILES_DISPACHER/Data/Input/CandidateInfo.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="Status" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Status!$A$1:$H$20</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -632,6 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -800,7 +804,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -904,7 +908,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -930,7 +934,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -956,7 +960,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1032,7 +1036,7 @@
       </c>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1110,7 +1114,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1136,7 +1140,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1163,6 +1167,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H20">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Hired"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
